--- a/backend/data/syllabus/Unit-Chapter List_ ICSE.xlsx
+++ b/backend/data/syllabus/Unit-Chapter List_ ICSE.xlsx
@@ -32,270 +32,849 @@
     <t>Newtonian Mechanics (10_ICSE)</t>
   </si>
   <si>
+    <t>Experimental Physics (09_ICSE)</t>
+  </si>
+  <si>
+    <t>Measurement and Experimentation</t>
+  </si>
+  <si>
     <t>Force</t>
   </si>
   <si>
+    <t>Newtonian Mechanics (09_ICSE)</t>
+  </si>
+  <si>
     <t>Work, Energy and Power</t>
   </si>
   <si>
+    <t>Motion in one dimension</t>
+  </si>
+  <si>
+    <t>Molecular Physics (08_ICSE)</t>
+  </si>
+  <si>
+    <t>Matter</t>
+  </si>
+  <si>
+    <t>Laws of motion</t>
+  </si>
+  <si>
     <t>Machines</t>
   </si>
   <si>
+    <t>Experimental Physics (08_ICSE)</t>
+  </si>
+  <si>
+    <t>Physical Quantities and Measurement</t>
+  </si>
+  <si>
     <t>Optics (10_ICSE)</t>
   </si>
   <si>
+    <t>Fluid Mechanics (09_ICSE)</t>
+  </si>
+  <si>
     <t>Refraction of Light at Plane Surfaces</t>
   </si>
   <si>
+    <t>Pressure in fluids and atmospheric pressure</t>
+  </si>
+  <si>
+    <t>Newtonian Mechanics (08_ICSE)</t>
+  </si>
+  <si>
+    <t>Force and Pressure</t>
+  </si>
+  <si>
     <t>Refraction Through Lens</t>
   </si>
   <si>
+    <t>Upthrust in Fluids, Archimedes’ Principle and Floatation</t>
+  </si>
+  <si>
+    <t>Experimental Physics (07_ICSE)</t>
+  </si>
+  <si>
     <t>Spectrum</t>
   </si>
   <si>
+    <t>Thermodynamics (09_ICSE)</t>
+  </si>
+  <si>
     <t>Waves Motion and its Propogation (10_ICSE)</t>
   </si>
   <si>
+    <t>Heat and Energy</t>
+  </si>
+  <si>
     <t>Sound</t>
   </si>
   <si>
+    <t>Newtonian Mechanics (07_ICSE)</t>
+  </si>
+  <si>
     <t>Electricity and Magnetism (10_ICSE)</t>
   </si>
   <si>
+    <t>Optics (09_ICSE)</t>
+  </si>
+  <si>
+    <t>Motion</t>
+  </si>
+  <si>
+    <t>Reflection of Light</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
     <t>Current Electricity</t>
   </si>
   <si>
+    <t>Waves Motion and its Propogation (09_ICSE)</t>
+  </si>
+  <si>
+    <t>Propagation of Sound waves</t>
+  </si>
+  <si>
+    <t>Optics (08_ICSE)</t>
+  </si>
+  <si>
     <t>Electrical Power and Household Circuits</t>
   </si>
   <si>
+    <t>Light Energy</t>
+  </si>
+  <si>
+    <t>Electricity and Magnetism (09_ICSE)</t>
+  </si>
+  <si>
+    <t>Optics (07_ICSE)</t>
+  </si>
+  <si>
+    <t>Thermodynamics (08_ICSE)</t>
+  </si>
+  <si>
     <t>Electro-Magnetism</t>
   </si>
   <si>
+    <t>Heat Transfer</t>
+  </si>
+  <si>
+    <t>Magnetism</t>
+  </si>
+  <si>
+    <t>Thermodynamics (07_ICSE)</t>
+  </si>
+  <si>
     <t>Thermodynamics (10_ICSE)</t>
   </si>
   <si>
+    <t>Waves Motion And Its Propogation (08_ICSE)</t>
+  </si>
+  <si>
     <t>Calorimetry</t>
   </si>
   <si>
+    <t>Heat</t>
+  </si>
+  <si>
     <t>Nuclear Physics (10_ICSE)</t>
   </si>
   <si>
     <t>Radioactivity</t>
   </si>
   <si>
+    <t>Electricity And Magnetism (08_ICSE)</t>
+  </si>
+  <si>
     <t>Chemistry</t>
   </si>
   <si>
+    <t>Electricity</t>
+  </si>
+  <si>
+    <t>Atomic Structure &amp; Language of Chemistry (09_ICSE) (09_ICSE)</t>
+  </si>
+  <si>
+    <t>Waves Motion And Its Propogation (07_ICSE)</t>
+  </si>
+  <si>
+    <t>The Language of Chemistry</t>
+  </si>
+  <si>
     <t>Atomic Structure &amp; Language of Chemistry (10_ICSE)</t>
   </si>
   <si>
     <t>Periodic Properties and Variations of Properties</t>
   </si>
   <si>
+    <t>Physical Chemistry (08_ICSE)</t>
+  </si>
+  <si>
+    <t>Chemical Changes and Reactions</t>
+  </si>
+  <si>
+    <t>Electricity And Magnetism (07_ICSE)</t>
+  </si>
+  <si>
+    <t>Electricity and magnetism</t>
+  </si>
+  <si>
     <t>Chemical bonding</t>
   </si>
   <si>
+    <t>Chemical Reactions and Changes (09_ICSE)</t>
+  </si>
+  <si>
+    <t>Chemical Reactions And Changes (08_ICSE)</t>
+  </si>
+  <si>
+    <t>Water</t>
+  </si>
+  <si>
+    <t>Physical and Chemical Changes</t>
+  </si>
+  <si>
+    <t>Matter (07_ICSE)</t>
+  </si>
+  <si>
     <t>Acids, Bases and Salts (10_ICSE)</t>
   </si>
   <si>
+    <t>Matter and its Composition</t>
+  </si>
+  <si>
     <t>Study of acids, bases and salts</t>
   </si>
   <si>
+    <t>Study of Compounds &amp; Elements (09_ICSE)</t>
+  </si>
+  <si>
+    <t>Atomic Structure &amp; Language Of Chemistry (08_ICSE)</t>
+  </si>
+  <si>
+    <t>Elements, Compounds and Mixtures</t>
+  </si>
+  <si>
+    <t>Atomic Structure and Chemical Bonding</t>
+  </si>
+  <si>
     <t>Analytical chemistry</t>
   </si>
   <si>
+    <t>Physical Chemistry (07_ICSE)</t>
+  </si>
+  <si>
     <t>Physical Chemistry (10_ICSE)</t>
   </si>
   <si>
+    <t>Atomic Structure</t>
+  </si>
+  <si>
+    <t>Metallurgy &amp; Periodic Table (09_ICSE)</t>
+  </si>
+  <si>
     <t>Mole concept and Stoichiometry</t>
   </si>
   <si>
+    <t>The periodic table</t>
+  </si>
+  <si>
+    <t>Study of the first Element Hydrogen</t>
+  </si>
+  <si>
+    <t>Language of Chemistry</t>
+  </si>
+  <si>
     <t>Electrolysis</t>
   </si>
   <si>
+    <t>Atomic Structure (07_ICSE)</t>
+  </si>
+  <si>
+    <t>Physical Chemistry (09_ICSE)</t>
+  </si>
+  <si>
+    <t>Study of Gas laws</t>
+  </si>
+  <si>
     <t>Metallurgy</t>
   </si>
   <si>
+    <t>Environmental Chemistry (09_ICSE)</t>
+  </si>
+  <si>
+    <t>Chemical Reactions</t>
+  </si>
+  <si>
+    <t>Language Of Chemistry (07_ICSE)</t>
+  </si>
+  <si>
+    <t>Atmospheric Pollution</t>
+  </si>
+  <si>
     <t>Study of Compounds &amp; Elements (10_ICSE)</t>
   </si>
   <si>
     <t>Hydrogen chloride</t>
   </si>
   <si>
+    <t>Biology</t>
+  </si>
+  <si>
+    <t>Diversity in Living Organisms (09_ICSE)</t>
+  </si>
+  <si>
+    <t>Introducing Biology</t>
+  </si>
+  <si>
+    <t>Study Of Compounds &amp; Elements (08_ICSE)</t>
+  </si>
+  <si>
+    <t>Metals And Non-Metals (07_ICSE)</t>
+  </si>
+  <si>
+    <t>The Cell (09_ICSE)</t>
+  </si>
+  <si>
     <t>Study of Compounds</t>
   </si>
   <si>
+    <t>Hydrogen</t>
+  </si>
+  <si>
+    <t>Metals and Non-Metals</t>
+  </si>
+  <si>
+    <t>Cell: The Unit Of Life</t>
+  </si>
+  <si>
     <t>Nitric acid</t>
   </si>
   <si>
+    <t>Tissues (09_ICSE)</t>
+  </si>
+  <si>
+    <t>Tissues: Plant And Animal Tissue</t>
+  </si>
+  <si>
+    <t>General Science (07_ICSE)</t>
+  </si>
+  <si>
+    <t>Air and Atmosphere</t>
+  </si>
+  <si>
     <t>Sulphuric acid</t>
   </si>
   <si>
+    <t>Reproduction &amp; Genetics (09_ICSE)</t>
+  </si>
+  <si>
+    <t>The Flower</t>
+  </si>
+  <si>
     <t>Carbon &amp; its Compounds (10_ICSE)</t>
   </si>
   <si>
+    <t>Tissues (07_ICSE)</t>
+  </si>
+  <si>
     <t>Organic chemistry</t>
   </si>
   <si>
-    <t>Biology</t>
+    <t>Plant and Animal Tissues</t>
+  </si>
+  <si>
+    <t>Carbon &amp; Its Compounds (08_ICSE)</t>
+  </si>
+  <si>
+    <t>Pollination and Fertilization</t>
+  </si>
+  <si>
+    <t>Carbon and its compounds</t>
   </si>
   <si>
     <t>The Cell (10_ICSE)</t>
   </si>
   <si>
+    <t>Seeds: Structure and Germination</t>
+  </si>
+  <si>
+    <t>Diversity In Living Organisms (07_ICSE)</t>
+  </si>
+  <si>
     <t>Cell – The Structural and Functional Unit of Life</t>
   </si>
   <si>
+    <t>Classification of Plants</t>
+  </si>
+  <si>
+    <t>Plant Anatomy and Physiology (09_ICSE)</t>
+  </si>
+  <si>
+    <t>Respiration in Plants</t>
+  </si>
+  <si>
+    <t>Plant Physiology (Transportation) (08_ICSE)</t>
+  </si>
+  <si>
     <t>Structure of Chromosomes, Cell Cycle and Cell Division</t>
   </si>
   <si>
+    <t>Transportation in Plants</t>
+  </si>
+  <si>
+    <t>Classification of Animals</t>
+  </si>
+  <si>
     <t>Reproduction &amp; Genetics (10_ICSE)</t>
   </si>
   <si>
+    <t>Five Kingdom Classification</t>
+  </si>
+  <si>
     <t>Genetics – Some Basic Fundamentals</t>
   </si>
   <si>
+    <t>Plant Physiology (07_ICSE)</t>
+  </si>
+  <si>
+    <t>Plant Physiology (Reproduction) (08_ICSE)</t>
+  </si>
+  <si>
     <t>Plant Anatomy and Physiology (10_ICSE)</t>
   </si>
   <si>
+    <t>Asexual Reproduction in Plant</t>
+  </si>
+  <si>
+    <t>Photosynthesis and Respiration</t>
+  </si>
+  <si>
+    <t>Economic Importance of Bacteria and Fungi</t>
+  </si>
+  <si>
     <t>Absorption by Roots – The Process Involved</t>
   </si>
   <si>
+    <t>Food &amp; Nutrition (09_ICSE)</t>
+  </si>
+  <si>
     <t>Transpiration</t>
   </si>
   <si>
+    <t>Nutrition</t>
+  </si>
+  <si>
+    <t>Human Anatomy And Physiology (07_ICSE)</t>
+  </si>
+  <si>
+    <t>Life Processes: Ingestion, Digestion, Absorption and Assimilation</t>
+  </si>
+  <si>
+    <t>Life Processes (09_ICSE)</t>
+  </si>
+  <si>
+    <t>Sexual Reproduction in Plants</t>
+  </si>
+  <si>
+    <t>Digestive system</t>
+  </si>
+  <si>
     <t>Photosynthesis</t>
   </si>
   <si>
+    <t>Excretion in Humans</t>
+  </si>
+  <si>
+    <t>Skeleton: Movement and Locomotion</t>
+  </si>
+  <si>
+    <t>Human Body (Reproduction) (08_ICSE)</t>
+  </si>
+  <si>
     <t>Chemical Coordination in Plants</t>
   </si>
   <si>
+    <t>Reproduction in Animals</t>
+  </si>
+  <si>
+    <t>Nervous System</t>
+  </si>
+  <si>
     <t>Life Processes (10_ICSE)</t>
   </si>
   <si>
+    <t>Skin: The Jack of all trades</t>
+  </si>
+  <si>
     <t>The Circulatory System</t>
   </si>
   <si>
+    <t>Health And Hygiene (07_ICSE)</t>
+  </si>
+  <si>
+    <t>The Respiratory System</t>
+  </si>
+  <si>
+    <t>Ecosystems (08_ICSE)</t>
+  </si>
+  <si>
+    <t>Allergy</t>
+  </si>
+  <si>
     <t>The Excretory System</t>
   </si>
   <si>
+    <t>Ecosystems</t>
+  </si>
+  <si>
+    <t>Mathematics</t>
+  </si>
+  <si>
     <t>The Nervous System</t>
   </si>
   <si>
+    <t>Number System (07_ICSE)</t>
+  </si>
+  <si>
+    <t>Microorganisms, Health &amp; Hygiene (09_ICSE)</t>
+  </si>
+  <si>
+    <t>Integers</t>
+  </si>
+  <si>
+    <t>Endocrine System and Adolescence</t>
+  </si>
+  <si>
     <t>Sense Organs</t>
   </si>
   <si>
+    <t>Hygiene: [A key to Healthy Life]</t>
+  </si>
+  <si>
+    <t>Rational Numbers</t>
+  </si>
+  <si>
     <t>The Endocrine System</t>
   </si>
   <si>
+    <t>Human Body (The Circulatory System) (08_ICSE)</t>
+  </si>
+  <si>
+    <t>Ratio &amp; Proportion (07_ICSE)</t>
+  </si>
+  <si>
+    <t>Diseases: Cause and Control</t>
+  </si>
+  <si>
+    <t>Fractions</t>
+  </si>
+  <si>
     <t>The Reproductive System</t>
   </si>
   <si>
+    <t>Human Body (Human Nervous System) (08_ICSE)</t>
+  </si>
+  <si>
+    <t>Aids to Health</t>
+  </si>
+  <si>
+    <t>Decimal Fractions</t>
+  </si>
+  <si>
+    <t>Human Nervous System</t>
+  </si>
+  <si>
     <t>Human Evolution</t>
   </si>
   <si>
     <t>Ecosystem (10_ICSE)</t>
   </si>
   <si>
+    <t>Health Organizations</t>
+  </si>
+  <si>
     <t>Population- the increasing numbers and rising problems</t>
   </si>
   <si>
+    <t>Exponents And Logarithm (07_ICSE)</t>
+  </si>
+  <si>
+    <t>Health And Hygiene (08_ICSE)</t>
+  </si>
+  <si>
+    <t>Exponents</t>
+  </si>
+  <si>
+    <t>Health and Hygiene</t>
+  </si>
+  <si>
+    <t>Ecosystem (09_ICSE)</t>
+  </si>
+  <si>
     <t>Pollution - A Rising Environmental problem</t>
   </si>
   <si>
-    <t>Mathematics</t>
+    <t>Waste Generation and Management</t>
+  </si>
+  <si>
+    <t>Set (07_ICSE)</t>
+  </si>
+  <si>
+    <t>Set Concepts</t>
   </si>
   <si>
     <t>Commercial Math (10_ICSE)</t>
   </si>
   <si>
+    <t>Food Production (08_ICSE)</t>
+  </si>
+  <si>
+    <t>Number System (09_ICSE)</t>
+  </si>
+  <si>
     <t>GST</t>
   </si>
   <si>
+    <t>Rational and Irrational Numbers</t>
+  </si>
+  <si>
+    <t>Food Production and Management</t>
+  </si>
+  <si>
+    <t>Ratio and Proportion</t>
+  </si>
+  <si>
     <t>Banking</t>
   </si>
   <si>
+    <t>Commercial Math (09_ICSE)</t>
+  </si>
+  <si>
+    <t>Compound Interest [Without Using Formula]</t>
+  </si>
+  <si>
+    <t>Unitary Method</t>
+  </si>
+  <si>
     <t>Shares and Dividend</t>
   </si>
   <si>
+    <t>Number System (08_ICSE)</t>
+  </si>
+  <si>
+    <t>Compound Interest [Using Formula]</t>
+  </si>
+  <si>
     <t>Equations and Inequalities (10_ICSE)</t>
   </si>
   <si>
     <t>Linear Inequations</t>
   </si>
   <si>
+    <t>Percent and Percentage</t>
+  </si>
+  <si>
+    <t>Algebraic Expressions (09_ICSE)</t>
+  </si>
+  <si>
     <t>Quadratic Equations</t>
   </si>
   <si>
+    <t>Expansions</t>
+  </si>
+  <si>
+    <t>Exponents And Logarithm (08_ICSE)</t>
+  </si>
+  <si>
+    <t>Commercial Math (07_ICSE)</t>
+  </si>
+  <si>
+    <t>Exponents Powers</t>
+  </si>
+  <si>
+    <t>Profit, Loss and Discount</t>
+  </si>
+  <si>
     <t>Ratio &amp; Proportion (10_ICSE)</t>
   </si>
   <si>
-    <t>Ratio and Proportion</t>
+    <t>Factorisation</t>
   </si>
   <si>
     <t>Playing with numbers (10_ICSE)</t>
   </si>
   <si>
+    <t>Simple Interest</t>
+  </si>
+  <si>
     <t>Remainder and Factor Theorems</t>
   </si>
   <si>
+    <t>Equations and Inequalities (09_ICSE)</t>
+  </si>
+  <si>
+    <t>Squares and Square Roots</t>
+  </si>
+  <si>
+    <t>Simultaneous Equations</t>
+  </si>
+  <si>
+    <t>Algebraic Expressions (07_ICSE)</t>
+  </si>
+  <si>
     <t>Matrices</t>
   </si>
   <si>
+    <t>Speed, Distance and Time</t>
+  </si>
+  <si>
     <t>Sequence and Series (10_ICSE)</t>
   </si>
   <si>
+    <t>Exponents and Logarithm (09_ICSE)</t>
+  </si>
+  <si>
+    <t>Cubes and Cube Roots</t>
+  </si>
+  <si>
     <t>Arithmetic Progression</t>
   </si>
   <si>
+    <t>Indices</t>
+  </si>
+  <si>
+    <t>Fundamental Concepts (Algebra)</t>
+  </si>
+  <si>
     <t>Geometric Progression</t>
   </si>
   <si>
+    <t>Logarithms</t>
+  </si>
+  <si>
+    <t>Equations And Inequalities (07_ICSE)</t>
+  </si>
+  <si>
+    <t>Playing With Number (08_ICSE)</t>
+  </si>
+  <si>
+    <t>Simple Linear Equations</t>
+  </si>
+  <si>
+    <t>Playing With Number</t>
+  </si>
+  <si>
     <t>Coordinate Geometry (10_ICSE)</t>
   </si>
   <si>
     <t>Coordinate Geometry – Reflection</t>
   </si>
   <si>
+    <t>Geometry (09_ICSE)</t>
+  </si>
+  <si>
+    <t>Triangles</t>
+  </si>
+  <si>
+    <t>Inequalities</t>
+  </si>
+  <si>
     <t>Section and Mid-Point Formula</t>
   </si>
   <si>
+    <t>Sets (08_ICSE)</t>
+  </si>
+  <si>
+    <t>Isosceles Triangles</t>
+  </si>
+  <si>
+    <t>Sets</t>
+  </si>
+  <si>
+    <t>Geometry (07_ICSE)</t>
+  </si>
+  <si>
     <t>Equation of a Line</t>
   </si>
   <si>
+    <t>Lines and Angles</t>
+  </si>
+  <si>
     <t>Mensuration (10_ICSE)</t>
   </si>
   <si>
     <t>Similarity</t>
   </si>
   <si>
+    <t>Ratio &amp; Proportion (08_ICSE)</t>
+  </si>
+  <si>
     <t>Geometry (10_ICSE)</t>
   </si>
   <si>
     <t>Loci</t>
   </si>
   <si>
+    <t>Midpoint and It’s Converse</t>
+  </si>
+  <si>
     <t>Circle: Arc and Cyclic Properties</t>
   </si>
   <si>
+    <t>Pythagoras Theorem</t>
+  </si>
+  <si>
+    <t>Commercial Math (08_ICSE)</t>
+  </si>
+  <si>
     <t>Circle: Tangents and Intersecting Chords</t>
   </si>
   <si>
+    <t>Profit Loss and Discount</t>
+  </si>
+  <si>
     <t>Circle: Constructions</t>
   </si>
   <si>
+    <t>Symmetry</t>
+  </si>
+  <si>
+    <t>Rectilinear Figures</t>
+  </si>
+  <si>
     <t>Mensuration: Cylinder, Cone and Sphere</t>
   </si>
   <si>
+    <t>Simple and Compound Interest</t>
+  </si>
+  <si>
     <t>Trigonometry (10_ICSE)</t>
   </si>
   <si>
+    <t>Recognition of Solids</t>
+  </si>
+  <si>
+    <t>Construction of Polygons</t>
+  </si>
+  <si>
     <t>Trigonometrical Identities</t>
   </si>
   <si>
     <t>Height and Distance</t>
   </si>
   <si>
+    <t>Coordinate Geometry (09_ICSE)</t>
+  </si>
+  <si>
+    <t>Direct and Inverse Variations</t>
+  </si>
+  <si>
+    <t>Area Theorems</t>
+  </si>
+  <si>
     <t>Statistics and Probability (10_ICSE)</t>
   </si>
   <si>
@@ -305,88 +884,304 @@
     <t>Measures of Central Tendency – Mean</t>
   </si>
   <si>
+    <t>Circle</t>
+  </si>
+  <si>
+    <t>Algebraic Expressions (08_ICSE)</t>
+  </si>
+  <si>
+    <t>Algebraic Expressions</t>
+  </si>
+  <si>
+    <t>Statistics and Probability (09_ICSE)</t>
+  </si>
+  <si>
     <t>Measures of Central Tendency – Median and Mode</t>
   </si>
   <si>
+    <t>Congruency: Congruent Triangles</t>
+  </si>
+  <si>
+    <t>Statistics</t>
+  </si>
+  <si>
     <t>Probability</t>
   </si>
   <si>
     <t>History</t>
   </si>
   <si>
+    <t>Constructions</t>
+  </si>
+  <si>
+    <t>Mean and Median</t>
+  </si>
+  <si>
     <t>COLONIALISM IN INDIA AND THE FREEDOM STRUGGLE (10_ICSE)</t>
   </si>
   <si>
     <t>The First War of Independence, 1857</t>
   </si>
   <si>
+    <t>Algebraic Identities</t>
+  </si>
+  <si>
+    <t>Mensuration (09_ICSE)</t>
+  </si>
+  <si>
+    <t>Mensuration (07_ICSE)</t>
+  </si>
+  <si>
+    <t>Area and Perimeter of Plane Figures</t>
+  </si>
+  <si>
+    <t>Mensuration</t>
+  </si>
+  <si>
+    <t>Statistics And Probability (07_ICSE)</t>
+  </si>
+  <si>
+    <t>Solids</t>
+  </si>
+  <si>
+    <t>Data Handling</t>
+  </si>
+  <si>
+    <t>Trigonometry (09_ICSE)</t>
+  </si>
+  <si>
+    <t>Equations And Inequalities (08_ICSE)</t>
+  </si>
+  <si>
+    <t>Trigonometrical Ratios</t>
+  </si>
+  <si>
     <t>Growth of Nationalism</t>
   </si>
   <si>
+    <t>Linear Equations in One Variable</t>
+  </si>
+  <si>
+    <t>Medieval World (07_ICSE)</t>
+  </si>
+  <si>
+    <t>The Medieval World</t>
+  </si>
+  <si>
+    <t>Trigonometrical Ratios of Standard Angles</t>
+  </si>
+  <si>
     <t>First Phase of the Indian National Movement</t>
   </si>
   <si>
+    <t>Christianity in Europe</t>
+  </si>
+  <si>
+    <t>Solutions of Right Triangles</t>
+  </si>
+  <si>
+    <t>Islam and its Impact</t>
+  </si>
+  <si>
+    <t>Geometry (08_ICSE)</t>
+  </si>
+  <si>
+    <t>Understanding Shapes</t>
+  </si>
+  <si>
     <t>Second Phase of Indian National Movement</t>
   </si>
   <si>
+    <t>The Turkish Invasions</t>
+  </si>
+  <si>
+    <t>Complementary Angles</t>
+  </si>
+  <si>
     <t>The Muslim League</t>
   </si>
   <si>
+    <t>Medieval India (07_ICSE)</t>
+  </si>
+  <si>
+    <t>The Delhi Sultanate</t>
+  </si>
+  <si>
+    <t>Special Types of Quadrilaterals</t>
+  </si>
+  <si>
+    <t>Coordinate Geometry</t>
+  </si>
+  <si>
     <t>Mahatma Gandhi and the National Movement</t>
   </si>
   <si>
+    <t>Cultural Developments Under The Delhi Sultanate</t>
+  </si>
+  <si>
+    <t>Graphical Solution</t>
+  </si>
+  <si>
     <t>Quit India Movement</t>
   </si>
   <si>
+    <t>The Vijayanagara and Bahmani Kingdoms</t>
+  </si>
+  <si>
+    <t>Distance Formula</t>
+  </si>
+  <si>
     <t>Forward Bloc and the INA</t>
   </si>
   <si>
+    <t>Mughal India - the Early Mughals and Sher Shah</t>
+  </si>
+  <si>
+    <t>Representing 3D in 2D</t>
+  </si>
+  <si>
+    <t>CIVILISATIONS (09_ICSE)</t>
+  </si>
+  <si>
+    <t>The Harappan Civilisation</t>
+  </si>
+  <si>
     <t>Independence and Partition of India</t>
   </si>
   <si>
     <t>MODERN WORLD HISTORY (10_ICSE)</t>
   </si>
   <si>
+    <t>Akbar (1556 to 1605 CE)</t>
+  </si>
+  <si>
     <t>The First World War</t>
   </si>
   <si>
+    <t>VEDIC PERIOD (09_ICSE)</t>
+  </si>
+  <si>
+    <t>Mensuration (08_ICSE)</t>
+  </si>
+  <si>
+    <t>The Vedic Period</t>
+  </si>
+  <si>
+    <t>Area of Trapezium and Polygon</t>
+  </si>
+  <si>
+    <t>Jahangir, Shah Jahan and Aurangazeb</t>
+  </si>
+  <si>
     <t>Rise of Dictatorships</t>
   </si>
   <si>
+    <t>BUDDHISM &amp; JAINISM (09_ICSE)</t>
+  </si>
+  <si>
+    <t>Jainism and Buddhism</t>
+  </si>
+  <si>
     <t>The Second World War</t>
   </si>
   <si>
+    <t>The Contributions of the Mughals to Indian Culture</t>
+  </si>
+  <si>
+    <t>ANCIENT INDIA (09_ICSE)</t>
+  </si>
+  <si>
     <t>United Nations</t>
   </si>
   <si>
+    <t>Surface Area, Volume and Capacity</t>
+  </si>
+  <si>
+    <t>The Mauryan Empire</t>
+  </si>
+  <si>
     <t>Major Agencies of the United Nations</t>
   </si>
   <si>
+    <t>Religious Developments in Medieval India</t>
+  </si>
+  <si>
+    <t>The Sangam Age</t>
+  </si>
+  <si>
     <t>Non-Aligned Movement</t>
   </si>
   <si>
+    <t>Statistics And Probability (08_ICSE)</t>
+  </si>
+  <si>
     <t>Civics</t>
   </si>
   <si>
+    <t>Constitution (07_ICSE)</t>
+  </si>
+  <si>
     <t>INSTITUTIONS (10_ICSE)</t>
   </si>
   <si>
+    <t>The Constitution of India</t>
+  </si>
+  <si>
     <t>The Union Parliament</t>
   </si>
   <si>
+    <t>The Age of the Guptas</t>
+  </si>
+  <si>
+    <t>The Directive Principles of State Policy</t>
+  </si>
+  <si>
+    <t>MEDIEVAL INDIA (09_ICSE)</t>
+  </si>
+  <si>
     <t>The President and the Vice President</t>
   </si>
   <si>
+    <t>Medieval India (a) The Cholas</t>
+  </si>
+  <si>
+    <t>Geography</t>
+  </si>
+  <si>
     <t>Prime Minister and Council of Ministers</t>
   </si>
   <si>
+    <t>Geographical Mapping And Interpretation Of Earth's Features (07_ICSE)</t>
+  </si>
+  <si>
+    <t>Representation of geographical features</t>
+  </si>
+  <si>
+    <t>Medieval India (b) The Delhi Sultanate</t>
+  </si>
+  <si>
     <t>The Supreme Court</t>
   </si>
   <si>
+    <t>Modern World History (08_ICSE)</t>
+  </si>
+  <si>
+    <t>Earth’s Domains And Atmosphere And Climate (07_ICSE)</t>
+  </si>
+  <si>
+    <t>A Period of Transition</t>
+  </si>
+  <si>
+    <t>the atmosphere</t>
+  </si>
+  <si>
+    <t>The Growth of Nationalism</t>
+  </si>
+  <si>
     <t>The High Courts and Subordinate Courts</t>
   </si>
   <si>
-    <t>Geography</t>
+    <t>Weather and Climate</t>
   </si>
   <si>
     <t>WASTE MANAGEMENT (10_ICSE)</t>
@@ -395,642 +1190,459 @@
     <t>Waste management I</t>
   </si>
   <si>
+    <t>Earth : It's Landforms , Movement And Structure (07_ICSE)</t>
+  </si>
+  <si>
+    <t>Napoleon Bonaparte and the Unification of Europe</t>
+  </si>
+  <si>
+    <t>Weathering and soil formation</t>
+  </si>
+  <si>
     <t>Waste management II</t>
   </si>
   <si>
+    <t>Medieval India (c) The Mughal Empire</t>
+  </si>
+  <si>
     <t>INTERACTION BETWEEN NATURAL AND HUMAN ENVIRONMENT (10_ICSE)</t>
   </si>
   <si>
+    <t>Industries (07_ICSE)</t>
+  </si>
+  <si>
     <t>Natural vegetation</t>
   </si>
   <si>
+    <t>Industries</t>
+  </si>
+  <si>
+    <t>The American Civil War</t>
+  </si>
+  <si>
     <t>LIFELINES OF NATIONAL ECONOMY (10_ICSE)</t>
   </si>
   <si>
     <t>Transport</t>
   </si>
   <si>
+    <t>Medieval India (d) Composite Culture</t>
+  </si>
+  <si>
+    <t>Natural And Human Resources : Management And Sustainability (07_ICSE)</t>
+  </si>
+  <si>
+    <t>Energy and power resources</t>
+  </si>
+  <si>
     <t>Hydrosphere : Water Systems and their Dynamics (10_ICSE)</t>
   </si>
   <si>
     <t>Water resources</t>
   </si>
   <si>
+    <t>Medieval India (08_ICSE)</t>
+  </si>
+  <si>
+    <t>MODERN WORLD HISTORY (09_ICSE)</t>
+  </si>
+  <si>
+    <t>India in the 18th Century</t>
+  </si>
+  <si>
+    <t>The Modern Age in Europe (a) Renaissance</t>
+  </si>
+  <si>
+    <t>Europe (07_ICSE)</t>
+  </si>
+  <si>
+    <t>Europe : Location , Political Divisions and Physical features</t>
+  </si>
+  <si>
     <t>EARTH’S DOMAINS AND ATMOSPHERE AND CLIMATE- (10_ICSE)</t>
   </si>
   <si>
     <t>Climate</t>
   </si>
   <si>
+    <t>The Modern Age in Europe (b) Reformation</t>
+  </si>
+  <si>
     <t>INDUSTRIES (10_ICSE)</t>
   </si>
   <si>
+    <t>Africa (07_ICSE)</t>
+  </si>
+  <si>
+    <t>Colonialism In India And The Freedom Struggle (08_ICSE)</t>
+  </si>
+  <si>
     <t>Manufacturing industries (Agro based)</t>
   </si>
   <si>
+    <t>Africa: Location , political divisions and physical features</t>
+  </si>
+  <si>
+    <t>From Traders to Rulers</t>
+  </si>
+  <si>
     <t>NATURAL AND HUMAN RESOURCES : MANAGEMENT AND SUSTAINABILITY (10_ICSE)</t>
   </si>
   <si>
+    <t>The Modern Age in Europe (c) Industrial Revolution</t>
+  </si>
+  <si>
     <t>Mineral based industry</t>
   </si>
   <si>
+    <t>Australia (07_ICSE)</t>
+  </si>
+  <si>
+    <t>Australia : Location, [Political divisions and physical features]</t>
+  </si>
+  <si>
+    <t>CONSTITUTION (09_ICSE)</t>
+  </si>
+  <si>
     <t>Conventional sources of energy</t>
   </si>
   <si>
+    <t>Our Constitution</t>
+  </si>
+  <si>
+    <t>The British Conquest of India - Part ! (1740-1765)</t>
+  </si>
+  <si>
+    <t>Antarctica (07_ICSE)</t>
+  </si>
+  <si>
+    <t>Antarctica : The Uninhabited Continent</t>
+  </si>
+  <si>
     <t>Non-Conventional sources of energy</t>
   </si>
   <si>
+    <t>Salient Features of The Constitution - I</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>Prose (07_ICSE)</t>
+  </si>
+  <si>
+    <t>An Uncomfortable Bed - Guy de Maupassant</t>
+  </si>
+  <si>
     <t>AGRICULTURE (10_ICSE)</t>
   </si>
   <si>
+    <t>Salient Features of The Constitution - II</t>
+  </si>
+  <si>
     <t>Agriculture-1</t>
   </si>
   <si>
+    <t>The British Conquest of India - Part !I (1765-1857)</t>
+  </si>
+  <si>
+    <t>DEMOCRACY (09_ICSE)</t>
+  </si>
+  <si>
+    <t>The Master Artist - Carol Moore</t>
+  </si>
+  <si>
+    <t>Elections</t>
+  </si>
+  <si>
     <t>Agriculture-II Food crops</t>
   </si>
   <si>
+    <t>LOCAL ADMINISTRATION (09_ICSE)</t>
+  </si>
+  <si>
+    <t>Poem (07_ICSE)</t>
+  </si>
+  <si>
+    <t>Local Self Government - Rural</t>
+  </si>
+  <si>
+    <t>Maps - Dorothy Brown Thompson</t>
+  </si>
+  <si>
     <t>Agriculture-III Cash crops (i)</t>
   </si>
   <si>
+    <t>Local Self Government - Urban</t>
+  </si>
+  <si>
+    <t>Homesickness - Roald Dahl</t>
+  </si>
+  <si>
     <t>Agriculture-IV Cash crops (ii)</t>
   </si>
   <si>
+    <t>Wandering Singers - Sarojini Naidu</t>
+  </si>
+  <si>
     <t>Soil resources</t>
   </si>
   <si>
+    <t>The Fight - Piri Thomas</t>
+  </si>
+  <si>
+    <t>The Impact of British Rule in India</t>
+  </si>
+  <si>
     <t>GEOGRAPHICAL MAPPING AND INTERPRETATION OF EARTH'S FEATURES (10_ICSE)</t>
   </si>
   <si>
+    <t>EARTH : IT'S LANDFORMS , MOVEMENT AND STRUCTURE (09_ICSE) (09_ICSE)</t>
+  </si>
+  <si>
+    <t>Vet in the Forest -  Dhriti K Lahiri-Choudhury</t>
+  </si>
+  <si>
     <t>Map of India</t>
   </si>
   <si>
+    <t>Earth as a Planet</t>
+  </si>
+  <si>
     <t>Interpretation of topographical maps</t>
   </si>
   <si>
+    <t>A Sea of Foliage - Toru Dutt</t>
+  </si>
+  <si>
+    <t>Socio-Religious Reforms</t>
+  </si>
+  <si>
+    <t>Latitudes and Longitudes</t>
+  </si>
+  <si>
+    <t>Zero Hour - Alexander Blade</t>
+  </si>
+  <si>
     <t>Location, extent and physical features</t>
   </si>
   <si>
+    <t>Rotation and Revolution</t>
+  </si>
+  <si>
+    <t>The Great Uprising of 1857</t>
+  </si>
+  <si>
+    <t>Friends and Flatterers - William Shakespeare</t>
+  </si>
+  <si>
     <t>Contours</t>
   </si>
   <si>
+    <t>Earth's Structure</t>
+  </si>
+  <si>
+    <t>Night Witches - Megan Garber</t>
+  </si>
+  <si>
+    <t>India's Struggle for Freedom (1858-1919)</t>
+  </si>
+  <si>
+    <t>Landforms of the Earth</t>
+  </si>
+  <si>
     <t>scales and directions</t>
   </si>
   <si>
+    <t>The Wolves of Cernogratz - Saki</t>
+  </si>
+  <si>
+    <t>Rocks and rock cycle</t>
+  </si>
+  <si>
     <t>Map reading and interpretation</t>
   </si>
   <si>
+    <t>Break, Break, Break - Alfred Lord Tennyson</t>
+  </si>
+  <si>
+    <t>Volcanoes</t>
+  </si>
+  <si>
+    <t>My Unknown Friend - Stephel Leacock</t>
+  </si>
+  <si>
     <t>Mineral resources</t>
   </si>
   <si>
-    <t>English</t>
+    <t>Earthquakes</t>
+  </si>
+  <si>
+    <t>The Mother Bird - Walter de la Mare</t>
   </si>
   <si>
     <t>PROSE (10_ICSE)</t>
   </si>
   <si>
+    <t>Weathering</t>
+  </si>
+  <si>
+    <t>The Kabuliwala - Rabindranath Tagore</t>
+  </si>
+  <si>
     <t>With the Photographer – Stephen Leacock</t>
   </si>
   <si>
+    <t>The Little Mechanic - Nathaniel Hawthorne</t>
+  </si>
+  <si>
+    <t>Denudation</t>
+  </si>
+  <si>
     <t>The Elevator – William Sleator</t>
   </si>
   <si>
+    <t>Heartwood - Robert - Macfarlane</t>
+  </si>
+  <si>
+    <t>Hydrosphere : Water Systems and their Dynamics  (09_ICSE) (09_ICSE)</t>
+  </si>
+  <si>
+    <t>Hydrosphere</t>
+  </si>
+  <si>
+    <t>Drama (07_ICSE)</t>
+  </si>
+  <si>
     <t>The Girl Who Can – Ama Ata Aidoo</t>
   </si>
   <si>
+    <t>The Play - William Shakespeare</t>
+  </si>
+  <si>
+    <t>EARTH’S DOMAINS AND ATMOSPHERE AND CLIMATE (09_ICSE) (09_ICSE)</t>
+  </si>
+  <si>
+    <t>Composition and Structure of the Atmosphere</t>
+  </si>
+  <si>
     <t>The Pedestrian – Ray Bradbury</t>
   </si>
   <si>
+    <t>Insolation</t>
+  </si>
+  <si>
+    <t>Atmospheric Pressure and Winds</t>
+  </si>
+  <si>
     <t>The Last Lesson – Alphonse Daudet</t>
   </si>
   <si>
     <t>POEM (10_ICSE)</t>
   </si>
   <si>
+    <t>Humidity</t>
+  </si>
+  <si>
     <t>Haunted Houses – H.W. Longfellow</t>
   </si>
   <si>
     <t>The Glove and the Lions – Leigh Hunt</t>
   </si>
   <si>
+    <t>POLLUTION (09_ICSE) (09_ICSE)</t>
+  </si>
+  <si>
+    <t>Pollution</t>
+  </si>
+  <si>
     <t>When Great Trees fall – Maya Angelou</t>
   </si>
   <si>
+    <t>Sources of Pollution</t>
+  </si>
+  <si>
+    <t>Effects of Pollution</t>
+  </si>
+  <si>
     <t>A Considerable Speck – Robert Frost</t>
   </si>
   <si>
+    <t>Pollution-Preventive Measures</t>
+  </si>
+  <si>
     <t>The Power of Music – Sukumar Ray</t>
   </si>
   <si>
     <t>DRAMA (10_ICSE)</t>
   </si>
   <si>
+    <t>INTERACTION BETWEEN NATURAL AND HUMAN ENVIRONMENT (09_ICSE) (09_ICSE)</t>
+  </si>
+  <si>
     <t>Julius Caesar: William Shakespeare Act III Scene 1</t>
   </si>
   <si>
+    <t>Natural Regions of the World</t>
+  </si>
+  <si>
     <t>Julius Caesar: William Shakespeare Act III Scene 2</t>
   </si>
   <si>
+    <t>PROSE (09_ICSE)</t>
+  </si>
+  <si>
     <t>Julius Caesar: William Shakespeare Act III Scene 3</t>
   </si>
   <si>
+    <t>Bonku Babu's Friend – Satyajit Ray</t>
+  </si>
+  <si>
     <t>Julius Caesar: William Shakespeare Act IV Scene 1</t>
   </si>
   <si>
+    <t>Oliver Asks for More – Charles Dickens</t>
+  </si>
+  <si>
     <t>Julius Caesar: William Shakespeare Act IV Scene 2</t>
   </si>
   <si>
+    <t>The Model Millionaire – Oscar Wilde</t>
+  </si>
+  <si>
     <t>Julius Caesar: William Shakespeare Act IV Scene 3</t>
   </si>
   <si>
     <t>Julius Caesar: William Shakespeare Act V Scene 1</t>
   </si>
   <si>
+    <t>Home-coming – Rabindranath Tagore</t>
+  </si>
+  <si>
     <t>Julius Caesar: William Shakespeare Act V Scene 2</t>
   </si>
   <si>
+    <t>The Boy who Broke the Bank – Ruskin Bond</t>
+  </si>
+  <si>
     <t>Julius Caesar: William Shakespeare Act V Scene 3</t>
   </si>
   <si>
+    <t>POEM (09_ICSE)</t>
+  </si>
+  <si>
+    <t>The Night Mail – W.H. Auden</t>
+  </si>
+  <si>
     <t>Julius Caesar: William Shakespeare Act V Scene 4</t>
   </si>
   <si>
+    <t>Skimbleshanks: The Railway Cat – T.S. Eliot</t>
+  </si>
+  <si>
     <t>Julius Caesar: William Shakespeare Act V Scene 5</t>
   </si>
   <si>
-    <t>Experimental Physics (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Measurement and Experimentation</t>
-  </si>
-  <si>
-    <t>Newtonian Mechanics (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Motion in one dimension</t>
-  </si>
-  <si>
-    <t>Laws of motion</t>
-  </si>
-  <si>
-    <t>Fluid Mechanics (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Pressure in fluids and atmospheric pressure</t>
-  </si>
-  <si>
-    <t>Upthrust in Fluids, Archimedes’ Principle and Floatation</t>
-  </si>
-  <si>
-    <t>Thermodynamics (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Heat and Energy</t>
-  </si>
-  <si>
-    <t>Optics (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Reflection of Light</t>
-  </si>
-  <si>
-    <t>Waves Motion and its Propogation (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Propagation of Sound waves</t>
-  </si>
-  <si>
-    <t>Electricity and Magnetism (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Magnetism</t>
-  </si>
-  <si>
-    <t>Atomic Structure &amp; Language of Chemistry (09_ICSE) (09_ICSE)</t>
-  </si>
-  <si>
-    <t>The Language of Chemistry</t>
-  </si>
-  <si>
-    <t>Chemical Changes and Reactions</t>
-  </si>
-  <si>
-    <t>Chemical Reactions and Changes (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Water</t>
-  </si>
-  <si>
-    <t>Study of Compounds &amp; Elements (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Atomic Structure and Chemical Bonding</t>
-  </si>
-  <si>
-    <t>Metallurgy &amp; Periodic Table (09_ICSE)</t>
-  </si>
-  <si>
-    <t>The periodic table</t>
-  </si>
-  <si>
-    <t>Study of the first Element Hydrogen</t>
-  </si>
-  <si>
-    <t>Physical Chemistry (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Study of Gas laws</t>
-  </si>
-  <si>
-    <t>Environmental Chemistry (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Atmospheric Pollution</t>
-  </si>
-  <si>
-    <t>Diversity in Living Organisms (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Introducing Biology</t>
-  </si>
-  <si>
-    <t>The Cell (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Cell: The Unit Of Life</t>
-  </si>
-  <si>
-    <t>Tissues (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Tissues: Plant And Animal Tissue</t>
-  </si>
-  <si>
-    <t>Reproduction &amp; Genetics (09_ICSE)</t>
-  </si>
-  <si>
-    <t>The Flower</t>
-  </si>
-  <si>
-    <t>Pollination and Fertilization</t>
-  </si>
-  <si>
-    <t>Seeds: Structure and Germination</t>
-  </si>
-  <si>
-    <t>Plant Anatomy and Physiology (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Respiration in Plants</t>
-  </si>
-  <si>
-    <t>Five Kingdom Classification</t>
-  </si>
-  <si>
-    <t>Economic Importance of Bacteria and Fungi</t>
-  </si>
-  <si>
-    <t>Food &amp; Nutrition (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Nutrition</t>
-  </si>
-  <si>
-    <t>Life Processes (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Digestive system</t>
-  </si>
-  <si>
-    <t>Skeleton: Movement and Locomotion</t>
-  </si>
-  <si>
-    <t>Skin: The Jack of all trades</t>
-  </si>
-  <si>
-    <t>The Respiratory System</t>
-  </si>
-  <si>
-    <t>Microorganisms, Health &amp; Hygiene (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Hygiene: [A key to Healthy Life]</t>
-  </si>
-  <si>
-    <t>Diseases: Cause and Control</t>
-  </si>
-  <si>
-    <t>Aids to Health</t>
-  </si>
-  <si>
-    <t>Health Organizations</t>
-  </si>
-  <si>
-    <t>Ecosystem (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Waste Generation and Management</t>
-  </si>
-  <si>
-    <t>Number System (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Rational and Irrational Numbers</t>
-  </si>
-  <si>
-    <t>Commercial Math (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Compound Interest [Without Using Formula]</t>
-  </si>
-  <si>
-    <t>Compound Interest [Using Formula]</t>
-  </si>
-  <si>
-    <t>Algebraic Expressions (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Expansions</t>
-  </si>
-  <si>
-    <t>Factorisation</t>
-  </si>
-  <si>
-    <t>Equations and Inequalities (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Simultaneous Equations</t>
-  </si>
-  <si>
-    <t>Exponents and Logarithm (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Indices</t>
-  </si>
-  <si>
-    <t>Logarithms</t>
-  </si>
-  <si>
-    <t>Geometry (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Triangles</t>
-  </si>
-  <si>
-    <t>Isosceles Triangles</t>
-  </si>
-  <si>
-    <t>Inequalities</t>
-  </si>
-  <si>
-    <t>Midpoint and It’s Converse</t>
-  </si>
-  <si>
-    <t>Pythagoras Theorem</t>
-  </si>
-  <si>
-    <t>Rectilinear Figures</t>
-  </si>
-  <si>
-    <t>Construction of Polygons</t>
-  </si>
-  <si>
-    <t>Coordinate Geometry (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Area Theorems</t>
-  </si>
-  <si>
-    <t>Circle</t>
-  </si>
-  <si>
-    <t>Statistics and Probability (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Statistics</t>
-  </si>
-  <si>
-    <t>Mean and Median</t>
-  </si>
-  <si>
-    <t>Mensuration (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Area and Perimeter of Plane Figures</t>
-  </si>
-  <si>
-    <t>Solids</t>
-  </si>
-  <si>
-    <t>Trigonometry (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Trigonometrical Ratios</t>
-  </si>
-  <si>
-    <t>Trigonometrical Ratios of Standard Angles</t>
-  </si>
-  <si>
-    <t>Solutions of Right Triangles</t>
-  </si>
-  <si>
-    <t>Complementary Angles</t>
-  </si>
-  <si>
-    <t>Coordinate Geometry</t>
-  </si>
-  <si>
-    <t>Graphical Solution</t>
-  </si>
-  <si>
-    <t>Distance Formula</t>
-  </si>
-  <si>
-    <t>CIVILISATIONS (09_ICSE)</t>
-  </si>
-  <si>
-    <t>The Harappan Civilisation</t>
-  </si>
-  <si>
-    <t>VEDIC PERIOD (09_ICSE)</t>
-  </si>
-  <si>
-    <t>The Vedic Period</t>
-  </si>
-  <si>
-    <t>BUDDHISM &amp; JAINISM (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Jainism and Buddhism</t>
-  </si>
-  <si>
-    <t>ANCIENT INDIA (09_ICSE)</t>
-  </si>
-  <si>
-    <t>The Mauryan Empire</t>
-  </si>
-  <si>
-    <t>The Sangam Age</t>
-  </si>
-  <si>
-    <t>The Age of the Guptas</t>
-  </si>
-  <si>
-    <t>MEDIEVAL INDIA (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Medieval India (a) The Cholas</t>
-  </si>
-  <si>
-    <t>Medieval India (b) The Delhi Sultanate</t>
-  </si>
-  <si>
-    <t>Medieval India (c) The Mughal Empire</t>
-  </si>
-  <si>
-    <t>Medieval India (d) Composite Culture</t>
-  </si>
-  <si>
-    <t>MODERN WORLD HISTORY (09_ICSE)</t>
-  </si>
-  <si>
-    <t>The Modern Age in Europe (a) Renaissance</t>
-  </si>
-  <si>
-    <t>The Modern Age in Europe (b) Reformation</t>
-  </si>
-  <si>
-    <t>The Modern Age in Europe (c) Industrial Revolution</t>
-  </si>
-  <si>
-    <t>CONSTITUTION (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Our Constitution</t>
-  </si>
-  <si>
-    <t>Salient Features of The Constitution - I</t>
-  </si>
-  <si>
-    <t>Salient Features of The Constitution - II</t>
-  </si>
-  <si>
-    <t>DEMOCRACY (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Elections</t>
-  </si>
-  <si>
-    <t>LOCAL ADMINISTRATION (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Local Self Government - Rural</t>
-  </si>
-  <si>
-    <t>Local Self Government - Urban</t>
-  </si>
-  <si>
-    <t>EARTH : IT'S LANDFORMS , MOVEMENT AND STRUCTURE (09_ICSE) (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Earth as a Planet</t>
-  </si>
-  <si>
-    <t>Latitudes and Longitudes</t>
-  </si>
-  <si>
-    <t>Rotation and Revolution</t>
-  </si>
-  <si>
-    <t>Earth's Structure</t>
-  </si>
-  <si>
-    <t>Landforms of the Earth</t>
-  </si>
-  <si>
-    <t>Rocks and rock cycle</t>
-  </si>
-  <si>
-    <t>Volcanoes</t>
-  </si>
-  <si>
-    <t>Earthquakes</t>
-  </si>
-  <si>
-    <t>Weathering</t>
-  </si>
-  <si>
-    <t>Denudation</t>
-  </si>
-  <si>
-    <t>Hydrosphere : Water Systems and their Dynamics  (09_ICSE) (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Hydrosphere</t>
-  </si>
-  <si>
-    <t>EARTH’S DOMAINS AND ATMOSPHERE AND CLIMATE (09_ICSE) (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Composition and Structure of the Atmosphere</t>
-  </si>
-  <si>
-    <t>Insolation</t>
-  </si>
-  <si>
-    <t>Atmospheric Pressure and Winds</t>
-  </si>
-  <si>
-    <t>Humidity</t>
-  </si>
-  <si>
-    <t>POLLUTION (09_ICSE) (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Pollution</t>
-  </si>
-  <si>
-    <t>Sources of Pollution</t>
-  </si>
-  <si>
-    <t>Effects of Pollution</t>
-  </si>
-  <si>
-    <t>Pollution-Preventive Measures</t>
-  </si>
-  <si>
-    <t>INTERACTION BETWEEN NATURAL AND HUMAN ENVIRONMENT (09_ICSE) (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Natural Regions of the World</t>
-  </si>
-  <si>
-    <t>PROSE (09_ICSE)</t>
-  </si>
-  <si>
-    <t>Bonku Babu's Friend – Satyajit Ray</t>
-  </si>
-  <si>
-    <t>Oliver Asks for More – Charles Dickens</t>
-  </si>
-  <si>
-    <t>The Model Millionaire – Oscar Wilde</t>
-  </si>
-  <si>
-    <t>Home-coming – Rabindranath Tagore</t>
-  </si>
-  <si>
-    <t>The Boy who Broke the Bank – Ruskin Bond</t>
-  </si>
-  <si>
-    <t>POEM (09_ICSE)</t>
-  </si>
-  <si>
-    <t>The Night Mail – W.H. Auden</t>
-  </si>
-  <si>
-    <t>Skimbleshanks: The Railway Cat – T.S. Eliot</t>
-  </si>
-  <si>
     <t>I Remember, I Remember – Thomas Hood</t>
   </si>
   <si>
@@ -1061,273 +1673,6 @@
     <t>Julius Caesar: William Shakespeare Act II Scene 3</t>
   </si>
   <si>
-    <t>Molecular Physics (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Matter</t>
-  </si>
-  <si>
-    <t>Experimental Physics (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Physical Quantities and Measurement</t>
-  </si>
-  <si>
-    <t>Newtonian Mechanics (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Force and Pressure</t>
-  </si>
-  <si>
-    <t>Energy</t>
-  </si>
-  <si>
-    <t>Optics (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Light Energy</t>
-  </si>
-  <si>
-    <t>Thermodynamics (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Heat Transfer</t>
-  </si>
-  <si>
-    <t>Waves Motion And Its Propogation (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Electricity And Magnetism (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Electricity</t>
-  </si>
-  <si>
-    <t>Physical Chemistry (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Chemical Reactions And Changes (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Physical and Chemical Changes</t>
-  </si>
-  <si>
-    <t>Atomic Structure &amp; Language Of Chemistry (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Elements, Compounds and Mixtures</t>
-  </si>
-  <si>
-    <t>Atomic Structure</t>
-  </si>
-  <si>
-    <t>Language of Chemistry</t>
-  </si>
-  <si>
-    <t>Chemical Reactions</t>
-  </si>
-  <si>
-    <t>Study Of Compounds &amp; Elements (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Hydrogen</t>
-  </si>
-  <si>
-    <t>Carbon &amp; Its Compounds (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Carbon and its compounds</t>
-  </si>
-  <si>
-    <t>Plant Physiology (Transportation) (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Transportation in Plants</t>
-  </si>
-  <si>
-    <t>Plant Physiology (Reproduction) (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Asexual Reproduction in Plant</t>
-  </si>
-  <si>
-    <t>Sexual Reproduction in Plants</t>
-  </si>
-  <si>
-    <t>Human Body (Reproduction) (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Reproduction in Animals</t>
-  </si>
-  <si>
-    <t>Ecosystems (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Ecosystems</t>
-  </si>
-  <si>
-    <t>Endocrine System and Adolescence</t>
-  </si>
-  <si>
-    <t>Human Body (The Circulatory System) (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Human Body (Human Nervous System) (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Human Nervous System</t>
-  </si>
-  <si>
-    <t>Health And Hygiene (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Health and Hygiene</t>
-  </si>
-  <si>
-    <t>Food Production (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Food Production and Management</t>
-  </si>
-  <si>
-    <t>Number System (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Rational Numbers</t>
-  </si>
-  <si>
-    <t>Exponents And Logarithm (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Exponents Powers</t>
-  </si>
-  <si>
-    <t>Squares and Square Roots</t>
-  </si>
-  <si>
-    <t>Cubes and Cube Roots</t>
-  </si>
-  <si>
-    <t>Playing With Number (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Playing With Number</t>
-  </si>
-  <si>
-    <t>Sets (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Sets</t>
-  </si>
-  <si>
-    <t>Ratio &amp; Proportion (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Percent and Percentage</t>
-  </si>
-  <si>
-    <t>Commercial Math (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Profit Loss and Discount</t>
-  </si>
-  <si>
-    <t>Simple and Compound Interest</t>
-  </si>
-  <si>
-    <t>Direct and Inverse Variations</t>
-  </si>
-  <si>
-    <t>Algebraic Expressions (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Algebraic Expressions</t>
-  </si>
-  <si>
-    <t>Algebraic Identities</t>
-  </si>
-  <si>
-    <t>Equations And Inequalities (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Linear Equations in One Variable</t>
-  </si>
-  <si>
-    <t>Geometry (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Understanding Shapes</t>
-  </si>
-  <si>
-    <t>Special Types of Quadrilaterals</t>
-  </si>
-  <si>
-    <t>Constructions</t>
-  </si>
-  <si>
-    <t>Representing 3D in 2D</t>
-  </si>
-  <si>
-    <t>Mensuration (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Area of Trapezium and Polygon</t>
-  </si>
-  <si>
-    <t>Surface Area, Volume and Capacity</t>
-  </si>
-  <si>
-    <t>Statistics And Probability (08_ICSE)</t>
-  </si>
-  <si>
-    <t>Data Handling</t>
-  </si>
-  <si>
-    <t>Modern World History (08_ICSE)</t>
-  </si>
-  <si>
-    <t>A Period of Transition</t>
-  </si>
-  <si>
-    <t>The Growth of Nationalism</t>
-  </si>
-  <si>
-    <t>Napoleon Bonaparte and the Unification of Europe</t>
-  </si>
-  <si>
-    <t>The American Civil War</t>
-  </si>
-  <si>
-    <t>Medieval India (08_ICSE)</t>
-  </si>
-  <si>
-    <t>India in the 18th Century</t>
-  </si>
-  <si>
-    <t>Colonialism In India And The Freedom Struggle (08_ICSE)</t>
-  </si>
-  <si>
-    <t>From Traders to Rulers</t>
-  </si>
-  <si>
-    <t>The British Conquest of India - Part ! (1740-1765)</t>
-  </si>
-  <si>
-    <t>The British Conquest of India - Part !I (1765-1857)</t>
-  </si>
-  <si>
-    <t>The Impact of British Rule in India</t>
-  </si>
-  <si>
-    <t>Socio-Religious Reforms</t>
-  </si>
-  <si>
-    <t>The Great Uprising of 1857</t>
-  </si>
-  <si>
-    <t>India's Struggle for Freedom (1858-1919)</t>
-  </si>
-  <si>
     <t>Mahatma Gandhi Leads the Freedom Struggle</t>
   </si>
   <si>
@@ -1394,9 +1739,6 @@
     <t>Geographical Mapping And Interpretation Of Earth's Features (08_ICSE)</t>
   </si>
   <si>
-    <t>Representation of geographical features</t>
-  </si>
-  <si>
     <t>Prose (08_ICSE)</t>
   </si>
   <si>
@@ -1458,348 +1800,6 @@
   </si>
   <si>
     <t>The Three Caskets -William Shakespeare</t>
-  </si>
-  <si>
-    <t>Experimental Physics (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Newtonian Mechanics (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Motion</t>
-  </si>
-  <si>
-    <t>Optics (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Thermodynamics (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Heat</t>
-  </si>
-  <si>
-    <t>Waves Motion And Its Propogation (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Electricity And Magnetism (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Electricity and magnetism</t>
-  </si>
-  <si>
-    <t>Matter (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Matter and its Composition</t>
-  </si>
-  <si>
-    <t>Physical Chemistry (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Atomic Structure (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Language Of Chemistry (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Metals And Non-Metals (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Metals and Non-Metals</t>
-  </si>
-  <si>
-    <t>General Science (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Air and Atmosphere</t>
-  </si>
-  <si>
-    <t>Tissues (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Plant and Animal Tissues</t>
-  </si>
-  <si>
-    <t>Diversity In Living Organisms (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Classification of Plants</t>
-  </si>
-  <si>
-    <t>Classification of Animals</t>
-  </si>
-  <si>
-    <t>Plant Physiology (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Photosynthesis and Respiration</t>
-  </si>
-  <si>
-    <t>Human Anatomy And Physiology (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Life Processes: Ingestion, Digestion, Absorption and Assimilation</t>
-  </si>
-  <si>
-    <t>Excretion in Humans</t>
-  </si>
-  <si>
-    <t>Nervous System</t>
-  </si>
-  <si>
-    <t>Health And Hygiene (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Allergy</t>
-  </si>
-  <si>
-    <t>Number System (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Integers</t>
-  </si>
-  <si>
-    <t>Ratio &amp; Proportion (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Fractions</t>
-  </si>
-  <si>
-    <t>Decimal Fractions</t>
-  </si>
-  <si>
-    <t>Exponents And Logarithm (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Exponents</t>
-  </si>
-  <si>
-    <t>Set (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Set Concepts</t>
-  </si>
-  <si>
-    <t>Unitary Method</t>
-  </si>
-  <si>
-    <t>Commercial Math (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Profit, Loss and Discount</t>
-  </si>
-  <si>
-    <t>Simple Interest</t>
-  </si>
-  <si>
-    <t>Algebraic Expressions (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Speed, Distance and Time</t>
-  </si>
-  <si>
-    <t>Fundamental Concepts (Algebra)</t>
-  </si>
-  <si>
-    <t>Equations And Inequalities (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Simple Linear Equations</t>
-  </si>
-  <si>
-    <t>Geometry (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Lines and Angles</t>
-  </si>
-  <si>
-    <t>Symmetry</t>
-  </si>
-  <si>
-    <t>Recognition of Solids</t>
-  </si>
-  <si>
-    <t>Congruency: Congruent Triangles</t>
-  </si>
-  <si>
-    <t>Mensuration (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Mensuration</t>
-  </si>
-  <si>
-    <t>Statistics And Probability (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Medieval World (07_ICSE)</t>
-  </si>
-  <si>
-    <t>The Medieval World</t>
-  </si>
-  <si>
-    <t>Christianity in Europe</t>
-  </si>
-  <si>
-    <t>Islam and its Impact</t>
-  </si>
-  <si>
-    <t>The Turkish Invasions</t>
-  </si>
-  <si>
-    <t>Medieval India (07_ICSE)</t>
-  </si>
-  <si>
-    <t>The Delhi Sultanate</t>
-  </si>
-  <si>
-    <t>Cultural Developments Under The Delhi Sultanate</t>
-  </si>
-  <si>
-    <t>The Vijayanagara and Bahmani Kingdoms</t>
-  </si>
-  <si>
-    <t>Mughal India - the Early Mughals and Sher Shah</t>
-  </si>
-  <si>
-    <t>Akbar (1556 to 1605 CE)</t>
-  </si>
-  <si>
-    <t>Jahangir, Shah Jahan and Aurangazeb</t>
-  </si>
-  <si>
-    <t>The Contributions of the Mughals to Indian Culture</t>
-  </si>
-  <si>
-    <t>Religious Developments in Medieval India</t>
-  </si>
-  <si>
-    <t>Constitution (07_ICSE)</t>
-  </si>
-  <si>
-    <t>The Constitution of India</t>
-  </si>
-  <si>
-    <t>The Directive Principles of State Policy</t>
-  </si>
-  <si>
-    <t>Geographical Mapping And Interpretation Of Earth's Features (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Earth’s Domains And Atmosphere And Climate (07_ICSE)</t>
-  </si>
-  <si>
-    <t>the atmosphere</t>
-  </si>
-  <si>
-    <t>Weather and Climate</t>
-  </si>
-  <si>
-    <t>Earth : It's Landforms , Movement And Structure (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Weathering and soil formation</t>
-  </si>
-  <si>
-    <t>Industries (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Industries</t>
-  </si>
-  <si>
-    <t>Natural And Human Resources : Management And Sustainability (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Energy and power resources</t>
-  </si>
-  <si>
-    <t>Europe (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Europe : Location , Political Divisions and Physical features</t>
-  </si>
-  <si>
-    <t>Africa (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Africa: Location , political divisions and physical features</t>
-  </si>
-  <si>
-    <t>Australia (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Australia : Location, [Political divisions and physical features]</t>
-  </si>
-  <si>
-    <t>Antarctica (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Antarctica : The Uninhabited Continent</t>
-  </si>
-  <si>
-    <t>Prose (07_ICSE)</t>
-  </si>
-  <si>
-    <t>An Uncomfortable Bed - Guy de Maupassant</t>
-  </si>
-  <si>
-    <t>The Master Artist - Carol Moore</t>
-  </si>
-  <si>
-    <t>Poem (07_ICSE)</t>
-  </si>
-  <si>
-    <t>Maps - Dorothy Brown Thompson</t>
-  </si>
-  <si>
-    <t>Homesickness - Roald Dahl</t>
-  </si>
-  <si>
-    <t>Wandering Singers - Sarojini Naidu</t>
-  </si>
-  <si>
-    <t>The Fight - Piri Thomas</t>
-  </si>
-  <si>
-    <t>Vet in the Forest -  Dhriti K Lahiri-Choudhury</t>
-  </si>
-  <si>
-    <t>A Sea of Foliage - Toru Dutt</t>
-  </si>
-  <si>
-    <t>Zero Hour - Alexander Blade</t>
-  </si>
-  <si>
-    <t>Friends and Flatterers - William Shakespeare</t>
-  </si>
-  <si>
-    <t>Night Witches - Megan Garber</t>
-  </si>
-  <si>
-    <t>The Wolves of Cernogratz - Saki</t>
-  </si>
-  <si>
-    <t>Break, Break, Break - Alfred Lord Tennyson</t>
-  </si>
-  <si>
-    <t>My Unknown Friend - Stephel Leacock</t>
-  </si>
-  <si>
-    <t>The Mother Bird - Walter de la Mare</t>
-  </si>
-  <si>
-    <t>The Kabuliwala - Rabindranath Tagore</t>
-  </si>
-  <si>
-    <t>The Little Mechanic - Nathaniel Hawthorne</t>
-  </si>
-  <si>
-    <t>Heartwood - Robert - Macfarlane</t>
-  </si>
-  <si>
-    <t>Drama (07_ICSE)</t>
-  </si>
-  <si>
-    <t>The Play - William Shakespeare</t>
   </si>
   <si>
     <t>Molecular Physics (06_ICSE)</t>
@@ -2443,7 +2443,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -2454,7 +2454,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -2465,7 +2465,7 @@
         <v>4</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -2473,10 +2473,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -2484,10 +2484,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -2495,10 +2495,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
@@ -2506,10 +2506,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
@@ -2517,10 +2517,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -2528,10 +2528,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
@@ -2539,10 +2539,10 @@
         <v>3</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
@@ -2550,10 +2550,10 @@
         <v>3</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
@@ -2561,1286 +2561,1286 @@
         <v>3</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>28</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>31</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>32</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>35</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>36</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>37</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>38</v>
+        <v>119</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>39</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>42</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>43</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>44</v>
+        <v>137</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>45</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>46</v>
+        <v>142</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>47</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>46</v>
+        <v>142</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>48</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>46</v>
+        <v>142</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>49</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>46</v>
+        <v>142</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>50</v>
+        <v>159</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>51</v>
+        <v>162</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>51</v>
+        <v>162</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>53</v>
+        <v>169</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>51</v>
+        <v>162</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>54</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>51</v>
+        <v>162</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>55</v>
+        <v>177</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>51</v>
+        <v>162</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>56</v>
+        <v>180</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>44</v>
+        <v>137</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>57</v>
+        <v>185</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>44</v>
+        <v>137</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>58</v>
+        <v>190</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>59</v>
+        <v>191</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>60</v>
+        <v>193</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>59</v>
+        <v>191</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>61</v>
+        <v>199</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>63</v>
+        <v>203</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>64</v>
+        <v>206</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>63</v>
+        <v>203</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>65</v>
+        <v>210</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>63</v>
+        <v>203</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>66</v>
+        <v>214</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>67</v>
+        <v>217</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>68</v>
+        <v>218</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>67</v>
+        <v>217</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>69</v>
+        <v>221</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>70</v>
+        <v>227</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>71</v>
+        <v>209</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>72</v>
+        <v>229</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>73</v>
+        <v>231</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>67</v>
+        <v>217</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>74</v>
+        <v>236</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>75</v>
+        <v>238</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>76</v>
+        <v>241</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>75</v>
+        <v>238</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>77</v>
+        <v>244</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>78</v>
+        <v>250</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>79</v>
+        <v>251</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>78</v>
+        <v>250</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>80</v>
+        <v>255</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>78</v>
+        <v>250</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>81</v>
+        <v>260</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>82</v>
+        <v>262</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>83</v>
+        <v>263</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>84</v>
+        <v>265</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>85</v>
+        <v>266</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>84</v>
+        <v>265</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>86</v>
+        <v>268</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>84</v>
+        <v>265</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>87</v>
+        <v>271</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>84</v>
+        <v>265</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>88</v>
+        <v>273</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>82</v>
+        <v>262</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>89</v>
+        <v>276</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>90</v>
+        <v>278</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>91</v>
+        <v>281</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>90</v>
+        <v>278</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>92</v>
+        <v>282</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>93</v>
+        <v>286</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>94</v>
+        <v>287</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>93</v>
+        <v>286</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>95</v>
+        <v>288</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>93</v>
+        <v>286</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>96</v>
+        <v>293</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>93</v>
+        <v>286</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>97</v>
+        <v>296</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>99</v>
+        <v>300</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>100</v>
+        <v>301</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>99</v>
+        <v>300</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>101</v>
+        <v>313</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>99</v>
+        <v>300</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>102</v>
+        <v>318</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>99</v>
+        <v>300</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>103</v>
+        <v>324</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>99</v>
+        <v>300</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>104</v>
+        <v>327</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>99</v>
+        <v>300</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>105</v>
+        <v>332</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>99</v>
+        <v>300</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>106</v>
+        <v>335</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>99</v>
+        <v>300</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>107</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>99</v>
+        <v>300</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>108</v>
+        <v>343</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>109</v>
+        <v>344</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>110</v>
+        <v>346</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>109</v>
+        <v>344</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>111</v>
+        <v>352</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>109</v>
+        <v>344</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>112</v>
+        <v>355</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>109</v>
+        <v>344</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>113</v>
+        <v>358</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>109</v>
+        <v>344</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>114</v>
+        <v>361</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>109</v>
+        <v>344</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>115</v>
+        <v>364</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>116</v>
+        <v>366</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>117</v>
+        <v>368</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>118</v>
+        <v>370</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>116</v>
+        <v>366</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>117</v>
+        <v>368</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>119</v>
+        <v>374</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>116</v>
+        <v>366</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>117</v>
+        <v>368</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>120</v>
+        <v>377</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>116</v>
+        <v>366</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>117</v>
+        <v>368</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>121</v>
+        <v>381</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>116</v>
+        <v>366</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>117</v>
+        <v>368</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>122</v>
+        <v>387</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>124</v>
+        <v>389</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>125</v>
+        <v>390</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>124</v>
+        <v>389</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>126</v>
+        <v>394</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>127</v>
+        <v>396</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>128</v>
+        <v>398</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>129</v>
+        <v>401</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>130</v>
+        <v>402</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>131</v>
+        <v>406</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>132</v>
+        <v>407</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>133</v>
+        <v>414</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>134</v>
+        <v>415</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>135</v>
+        <v>417</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>136</v>
+        <v>420</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>137</v>
+        <v>423</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>138</v>
+        <v>425</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>137</v>
+        <v>423</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>139</v>
+        <v>429</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>137</v>
+        <v>423</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>140</v>
+        <v>434</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>141</v>
+        <v>439</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>142</v>
+        <v>441</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>141</v>
+        <v>439</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>143</v>
+        <v>446</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>141</v>
+        <v>439</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>144</v>
+        <v>451</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>141</v>
+        <v>439</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>145</v>
+        <v>454</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>137</v>
+        <v>423</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>146</v>
+        <v>456</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>147</v>
+        <v>459</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>148</v>
+        <v>462</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>147</v>
+        <v>459</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>149</v>
+        <v>464</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>147</v>
+        <v>459</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>150</v>
+        <v>469</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>147</v>
+        <v>459</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>151</v>
+        <v>473</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>147</v>
+        <v>459</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>152</v>
+        <v>478</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>147</v>
+        <v>459</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>153</v>
+        <v>481</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>137</v>
+        <v>423</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>154</v>
+        <v>485</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>156</v>
+        <v>488</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>157</v>
+        <v>491</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>156</v>
+        <v>488</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>158</v>
+        <v>494</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>156</v>
+        <v>488</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>159</v>
+        <v>499</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>156</v>
+        <v>488</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>160</v>
+        <v>503</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>156</v>
+        <v>488</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>161</v>
+        <v>506</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>162</v>
+        <v>507</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>163</v>
+        <v>509</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>162</v>
+        <v>507</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>164</v>
+        <v>510</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>162</v>
+        <v>507</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>165</v>
+        <v>513</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>162</v>
+        <v>507</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>166</v>
+        <v>516</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>162</v>
+        <v>507</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>167</v>
+        <v>518</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>168</v>
+        <v>519</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>169</v>
+        <v>521</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>168</v>
+        <v>519</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>170</v>
+        <v>523</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>168</v>
+        <v>519</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>171</v>
+        <v>525</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>168</v>
+        <v>519</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>172</v>
+        <v>527</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>168</v>
+        <v>519</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>173</v>
+        <v>529</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>168</v>
+        <v>519</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>174</v>
+        <v>531</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>168</v>
+        <v>519</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>175</v>
+        <v>532</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>168</v>
+        <v>519</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>176</v>
+        <v>534</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>168</v>
+        <v>519</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>177</v>
+        <v>536</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>168</v>
+        <v>519</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>178</v>
+        <v>539</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>168</v>
+        <v>519</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>179</v>
+        <v>541</v>
       </c>
     </row>
   </sheetData>
@@ -3894,10 +3894,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>180</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>181</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -3905,10 +3905,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>182</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>183</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -3916,10 +3916,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>182</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>184</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -3927,10 +3927,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>185</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>186</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -3938,10 +3938,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>185</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>187</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -3949,10 +3949,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>188</v>
+        <v>27</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>189</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -3960,10 +3960,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>190</v>
+        <v>33</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>191</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
@@ -3971,10 +3971,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>192</v>
+        <v>38</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>193</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -3982,10 +3982,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>194</v>
+        <v>43</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
@@ -3993,425 +3993,425 @@
         <v>3</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>194</v>
+        <v>43</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>195</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>196</v>
+        <v>59</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>197</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>196</v>
+        <v>59</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>198</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>199</v>
+        <v>69</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>200</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>202</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>203</v>
+        <v>85</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>204</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>205</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>206</v>
+        <v>92</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>207</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>208</v>
+        <v>95</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>209</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>210</v>
+        <v>102</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>211</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>212</v>
+        <v>106</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>213</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>214</v>
+        <v>112</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>215</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>216</v>
+        <v>117</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>217</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>216</v>
+        <v>117</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>218</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>216</v>
+        <v>117</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>219</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>220</v>
+        <v>131</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>221</v>
+        <v>132</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>210</v>
+        <v>102</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>222</v>
+        <v>138</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>210</v>
+        <v>102</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>223</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>224</v>
+        <v>147</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>225</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>226</v>
+        <v>152</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>227</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>226</v>
+        <v>152</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>228</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>226</v>
+        <v>152</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>229</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>226</v>
+        <v>152</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>230</v>
+        <v>166</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>231</v>
+        <v>174</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>232</v>
+        <v>178</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>231</v>
+        <v>174</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>233</v>
+        <v>183</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>231</v>
+        <v>174</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>234</v>
+        <v>187</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>231</v>
+        <v>174</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>235</v>
+        <v>192</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>236</v>
+        <v>198</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>237</v>
+        <v>200</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>239</v>
+        <v>207</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>240</v>
+        <v>211</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>241</v>
+        <v>212</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>240</v>
+        <v>211</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>242</v>
+        <v>216</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>254</v>
@@ -4419,794 +4419,794 @@
     </row>
     <row r="50">
       <c r="A50" s="5" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>260</v>
+        <v>285</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>261</v>
+        <v>289</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>263</v>
+        <v>295</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>265</v>
+        <v>303</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>266</v>
+        <v>305</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>265</v>
+        <v>303</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>267</v>
+        <v>308</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>268</v>
+        <v>310</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>269</v>
+        <v>312</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>268</v>
+        <v>310</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>270</v>
+        <v>317</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>271</v>
+        <v>320</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>272</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>273</v>
+        <v>331</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>274</v>
+        <v>334</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>275</v>
+        <v>337</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>276</v>
+        <v>341</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>277</v>
+        <v>342</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>278</v>
+        <v>347</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>279</v>
+        <v>349</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>280</v>
+        <v>353</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>281</v>
+        <v>354</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>282</v>
+        <v>357</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>283</v>
+        <v>360</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>282</v>
+        <v>357</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>284</v>
+        <v>363</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>282</v>
+        <v>357</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>285</v>
+        <v>371</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>286</v>
+        <v>373</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>287</v>
+        <v>375</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>286</v>
+        <v>373</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>288</v>
+        <v>380</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>286</v>
+        <v>373</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>289</v>
+        <v>395</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>286</v>
+        <v>373</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>290</v>
+        <v>403</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>291</v>
+        <v>409</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>292</v>
+        <v>411</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>291</v>
+        <v>409</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>293</v>
+        <v>416</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>291</v>
+        <v>409</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>294</v>
+        <v>424</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>116</v>
+        <v>366</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>295</v>
+        <v>428</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>296</v>
+        <v>430</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>116</v>
+        <v>366</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>295</v>
+        <v>428</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>297</v>
+        <v>435</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>116</v>
+        <v>366</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>295</v>
+        <v>428</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>298</v>
+        <v>440</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>116</v>
+        <v>366</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>299</v>
+        <v>443</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>300</v>
+        <v>445</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>116</v>
+        <v>366</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>301</v>
+        <v>447</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>302</v>
+        <v>449</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>116</v>
+        <v>366</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>301</v>
+        <v>447</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>303</v>
+        <v>452</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>304</v>
+        <v>460</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>305</v>
+        <v>463</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>304</v>
+        <v>460</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>306</v>
+        <v>467</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>304</v>
+        <v>460</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>307</v>
+        <v>470</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>304</v>
+        <v>460</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>308</v>
+        <v>474</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>304</v>
+        <v>460</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>309</v>
+        <v>477</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>304</v>
+        <v>460</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>310</v>
+        <v>480</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>304</v>
+        <v>460</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>311</v>
+        <v>483</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>304</v>
+        <v>460</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>312</v>
+        <v>486</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>304</v>
+        <v>460</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>313</v>
+        <v>489</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>304</v>
+        <v>460</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>314</v>
+        <v>493</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>315</v>
+        <v>496</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>316</v>
+        <v>497</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>317</v>
+        <v>501</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>318</v>
+        <v>502</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>317</v>
+        <v>501</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>319</v>
+        <v>504</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>317</v>
+        <v>501</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>320</v>
+        <v>505</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>317</v>
+        <v>501</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>321</v>
+        <v>508</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>322</v>
+        <v>511</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>323</v>
+        <v>512</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>322</v>
+        <v>511</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>324</v>
+        <v>514</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>322</v>
+        <v>511</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>325</v>
+        <v>515</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>322</v>
+        <v>511</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>326</v>
+        <v>517</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>327</v>
+        <v>520</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>328</v>
+        <v>522</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>329</v>
+        <v>524</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>330</v>
+        <v>526</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>329</v>
+        <v>524</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>331</v>
+        <v>528</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>329</v>
+        <v>524</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>332</v>
+        <v>530</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>329</v>
+        <v>524</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>333</v>
+        <v>533</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>329</v>
+        <v>524</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>334</v>
+        <v>535</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>335</v>
+        <v>537</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>336</v>
+        <v>538</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>335</v>
+        <v>537</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>337</v>
+        <v>540</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>335</v>
+        <v>537</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>338</v>
+        <v>542</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>335</v>
+        <v>537</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>339</v>
+        <v>543</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>335</v>
+        <v>537</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>340</v>
+        <v>544</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>341</v>
+        <v>545</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>342</v>
+        <v>546</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>341</v>
+        <v>545</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>343</v>
+        <v>547</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>341</v>
+        <v>545</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>344</v>
+        <v>548</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>341</v>
+        <v>545</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>345</v>
+        <v>549</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>341</v>
+        <v>545</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>346</v>
+        <v>550</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>341</v>
+        <v>545</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>347</v>
+        <v>551</v>
       </c>
     </row>
   </sheetData>
@@ -5260,10 +5260,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>348</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>349</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -5271,10 +5271,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>350</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>351</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -5282,10 +5282,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>352</v>
+        <v>21</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>353</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -5293,10 +5293,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>352</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>354</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
@@ -5304,10 +5304,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>355</v>
+        <v>40</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>356</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -5315,10 +5315,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>357</v>
+        <v>45</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>358</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8">
@@ -5326,10 +5326,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>359</v>
+        <v>51</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
@@ -5337,546 +5337,546 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>360</v>
+        <v>56</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>361</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>362</v>
+        <v>64</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>349</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>363</v>
+        <v>70</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>364</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>365</v>
+        <v>78</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>366</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>365</v>
+        <v>78</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>367</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>365</v>
+        <v>78</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>368</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>363</v>
+        <v>70</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>369</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>370</v>
+        <v>104</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>371</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>370</v>
+        <v>104</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>200</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>372</v>
+        <v>123</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>373</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>374</v>
+        <v>133</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>375</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>376</v>
+        <v>141</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>377</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>376</v>
+        <v>141</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>378</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>379</v>
+        <v>158</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>380</v>
+        <v>160</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>381</v>
+        <v>167</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>382</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>379</v>
+        <v>158</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>383</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>384</v>
+        <v>181</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>385</v>
+        <v>186</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>386</v>
+        <v>189</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>387</v>
+        <v>195</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>388</v>
+        <v>197</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>389</v>
+        <v>204</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>390</v>
+        <v>208</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>391</v>
+        <v>215</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>392</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>393</v>
+        <v>223</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>394</v>
+        <v>225</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>393</v>
+        <v>223</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>395</v>
+        <v>233</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>393</v>
+        <v>223</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>396</v>
+        <v>240</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>397</v>
+        <v>247</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>398</v>
+        <v>249</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>399</v>
+        <v>256</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>400</v>
+        <v>258</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>401</v>
+        <v>264</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>402</v>
+        <v>219</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>403</v>
+        <v>270</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>404</v>
+        <v>272</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>403</v>
+        <v>270</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>405</v>
+        <v>277</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>401</v>
+        <v>264</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>406</v>
+        <v>284</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>407</v>
+        <v>290</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>408</v>
+        <v>291</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>407</v>
+        <v>290</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>409</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>407</v>
+        <v>290</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>410</v>
+        <v>311</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>411</v>
+        <v>314</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>410</v>
+        <v>311</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>68</v>
+        <v>218</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>412</v>
+        <v>322</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>413</v>
+        <v>323</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>412</v>
+        <v>322</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>414</v>
+        <v>330</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>412</v>
+        <v>322</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>415</v>
+        <v>298</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>412</v>
+        <v>322</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>416</v>
+        <v>340</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>417</v>
+        <v>348</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>418</v>
+        <v>350</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>417</v>
+        <v>348</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>419</v>
+        <v>359</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>420</v>
+        <v>365</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>421</v>
+        <v>309</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>420</v>
+        <v>365</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>97</v>
+        <v>296</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>422</v>
+        <v>382</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>423</v>
+        <v>384</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>422</v>
+        <v>382</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>424</v>
+        <v>386</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>422</v>
+        <v>382</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>425</v>
+        <v>392</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>422</v>
+        <v>382</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>426</v>
+        <v>400</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>427</v>
+        <v>408</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>428</v>
+        <v>410</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>431</v>
@@ -5884,431 +5884,431 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>433</v>
+        <v>458</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>434</v>
+        <v>466</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>436</v>
+        <v>476</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>437</v>
+        <v>552</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>438</v>
+        <v>553</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>116</v>
+        <v>366</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>439</v>
+        <v>554</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>440</v>
+        <v>555</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>116</v>
+        <v>366</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>439</v>
+        <v>554</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>441</v>
+        <v>556</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>116</v>
+        <v>366</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>442</v>
+        <v>557</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>443</v>
+        <v>558</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>444</v>
+        <v>559</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>445</v>
+        <v>560</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>446</v>
+        <v>561</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>447</v>
+        <v>562</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>448</v>
+        <v>563</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>449</v>
+        <v>564</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>446</v>
+        <v>561</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>450</v>
+        <v>565</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>446</v>
+        <v>561</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>451</v>
+        <v>566</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>452</v>
+        <v>567</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>453</v>
+        <v>568</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>452</v>
+        <v>567</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>454</v>
+        <v>569</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>455</v>
+        <v>570</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>456</v>
+        <v>571</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>455</v>
+        <v>570</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>457</v>
+        <v>572</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>458</v>
+        <v>573</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>459</v>
+        <v>379</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>460</v>
+        <v>574</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>334</v>
+        <v>535</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>461</v>
+        <v>575</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>462</v>
+        <v>576</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>460</v>
+        <v>574</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>463</v>
+        <v>577</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>460</v>
+        <v>574</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>464</v>
+        <v>578</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>461</v>
+        <v>575</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>465</v>
+        <v>579</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>460</v>
+        <v>574</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>466</v>
+        <v>580</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>460</v>
+        <v>574</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>467</v>
+        <v>581</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>461</v>
+        <v>575</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>468</v>
+        <v>582</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>460</v>
+        <v>574</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>469</v>
+        <v>583</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>460</v>
+        <v>574</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>470</v>
+        <v>584</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>461</v>
+        <v>575</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>471</v>
+        <v>585</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>460</v>
+        <v>574</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>472</v>
+        <v>586</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>460</v>
+        <v>574</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>473</v>
+        <v>587</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>461</v>
+        <v>575</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>474</v>
+        <v>588</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>460</v>
+        <v>574</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>475</v>
+        <v>589</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>461</v>
+        <v>575</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>476</v>
+        <v>590</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>460</v>
+        <v>574</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>477</v>
+        <v>591</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>461</v>
+        <v>575</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>478</v>
+        <v>592</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>479</v>
+        <v>593</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>480</v>
+        <v>594</v>
       </c>
     </row>
   </sheetData>
@@ -6362,10 +6362,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>481</v>
+        <v>25</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>351</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -6373,10 +6373,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>482</v>
+        <v>31</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>483</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -6384,10 +6384,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>482</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>354</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -6395,10 +6395,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>484</v>
+        <v>44</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>356</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
@@ -6406,10 +6406,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>485</v>
+        <v>49</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>486</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
@@ -6417,10 +6417,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>487</v>
+        <v>60</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -6428,337 +6428,337 @@
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>488</v>
+        <v>66</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>489</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>490</v>
+        <v>73</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>491</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>492</v>
+        <v>82</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>364</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>492</v>
+        <v>82</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>366</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>493</v>
+        <v>91</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>367</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>494</v>
+        <v>97</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>368</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>495</v>
+        <v>105</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>496</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>497</v>
+        <v>114</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>498</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>499</v>
+        <v>120</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>500</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>501</v>
+        <v>128</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>502</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>501</v>
+        <v>128</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>503</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>504</v>
+        <v>140</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>505</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>506</v>
+        <v>150</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>507</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>506</v>
+        <v>150</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>508</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>506</v>
+        <v>150</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>509</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>510</v>
+        <v>165</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>511</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>512</v>
+        <v>173</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>513</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>512</v>
+        <v>173</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>392</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>514</v>
+        <v>182</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>515</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>514</v>
+        <v>182</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>516</v>
+        <v>188</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>517</v>
+        <v>194</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>518</v>
+        <v>196</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>519</v>
+        <v>201</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>520</v>
+        <v>202</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>514</v>
+        <v>182</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>71</v>
+        <v>209</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>514</v>
+        <v>182</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>521</v>
+        <v>213</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>514</v>
+        <v>182</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>402</v>
+        <v>219</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>522</v>
+        <v>224</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>523</v>
+        <v>226</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>522</v>
+        <v>224</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>524</v>
+        <v>230</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>525</v>
+        <v>235</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>526</v>
+        <v>237</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>525</v>
+        <v>235</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>527</v>
+        <v>243</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>528</v>
+        <v>246</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>529</v>
+        <v>248</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>528</v>
+        <v>246</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>254</v>
@@ -6766,585 +6766,585 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>530</v>
+        <v>259</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>531</v>
+        <v>261</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>530</v>
+        <v>259</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>530</v>
+        <v>259</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>530</v>
+        <v>259</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>532</v>
+        <v>274</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>530</v>
+        <v>259</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>533</v>
+        <v>279</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>530</v>
+        <v>259</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>534</v>
+        <v>294</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>530</v>
+        <v>259</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>415</v>
+        <v>298</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>535</v>
+        <v>304</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>536</v>
+        <v>306</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>537</v>
+        <v>307</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>421</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>537</v>
+        <v>307</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>97</v>
+        <v>296</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>538</v>
+        <v>315</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>539</v>
+        <v>316</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>538</v>
+        <v>315</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>540</v>
+        <v>319</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>538</v>
+        <v>315</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>541</v>
+        <v>321</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>538</v>
+        <v>315</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>542</v>
+        <v>325</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>543</v>
+        <v>328</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>544</v>
+        <v>329</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>543</v>
+        <v>328</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>545</v>
+        <v>333</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>543</v>
+        <v>328</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>546</v>
+        <v>336</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>543</v>
+        <v>328</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>547</v>
+        <v>339</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>543</v>
+        <v>328</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>548</v>
+        <v>345</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>543</v>
+        <v>328</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>549</v>
+        <v>351</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>543</v>
+        <v>328</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>550</v>
+        <v>356</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>543</v>
+        <v>328</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>551</v>
+        <v>362</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>116</v>
+        <v>366</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>552</v>
+        <v>367</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>553</v>
+        <v>369</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>116</v>
+        <v>366</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>552</v>
+        <v>367</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>554</v>
+        <v>372</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>555</v>
+        <v>378</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>459</v>
+        <v>379</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>556</v>
+        <v>383</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>557</v>
+        <v>385</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>556</v>
+        <v>383</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>558</v>
+        <v>388</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>559</v>
+        <v>391</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>560</v>
+        <v>393</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>561</v>
+        <v>397</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>562</v>
+        <v>399</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>563</v>
+        <v>404</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>564</v>
+        <v>405</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>565</v>
+        <v>412</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>566</v>
+        <v>413</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>567</v>
+        <v>418</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>568</v>
+        <v>421</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>569</v>
+        <v>426</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>570</v>
+        <v>427</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>571</v>
+        <v>432</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>572</v>
+        <v>433</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>573</v>
+        <v>437</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>574</v>
+        <v>438</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>573</v>
+        <v>437</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>575</v>
+        <v>444</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>576</v>
+        <v>448</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>577</v>
+        <v>450</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>573</v>
+        <v>437</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>578</v>
+        <v>453</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>576</v>
+        <v>448</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>579</v>
+        <v>455</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>573</v>
+        <v>437</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>580</v>
+        <v>457</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>573</v>
+        <v>437</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>581</v>
+        <v>461</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>576</v>
+        <v>448</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>582</v>
+        <v>465</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>573</v>
+        <v>437</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>583</v>
+        <v>468</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>576</v>
+        <v>448</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>584</v>
+        <v>472</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>573</v>
+        <v>437</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>585</v>
+        <v>475</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>573</v>
+        <v>437</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>586</v>
+        <v>479</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>576</v>
+        <v>448</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>587</v>
+        <v>482</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>573</v>
+        <v>437</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>588</v>
+        <v>484</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>576</v>
+        <v>448</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>589</v>
+        <v>487</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>573</v>
+        <v>437</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>590</v>
+        <v>490</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>573</v>
+        <v>437</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>591</v>
+        <v>492</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>576</v>
+        <v>448</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>592</v>
+        <v>495</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>593</v>
+        <v>498</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>594</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -7401,7 +7401,7 @@
         <v>595</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>349</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -7423,7 +7423,7 @@
         <v>598</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -7456,12 +7456,12 @@
         <v>602</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>195</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>603</v>
@@ -7472,7 +7472,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>603</v>
@@ -7483,18 +7483,18 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>606</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>349</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>607</v>
@@ -7505,7 +7505,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>609</v>
@@ -7516,29 +7516,29 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>603</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>498</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>603</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>200</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>611</v>
@@ -7549,18 +7549,18 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>611</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>217</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>613</v>
@@ -7571,7 +7571,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>615</v>
@@ -7582,7 +7582,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>615</v>
@@ -7593,29 +7593,29 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>615</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>618</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>388</v>
+        <v>197</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>619</v>
@@ -7626,7 +7626,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>621</v>
@@ -7637,7 +7637,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>621</v>
@@ -7648,7 +7648,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>624</v>
@@ -7659,40 +7659,40 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>626</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>400</v>
+        <v>258</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>621</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>515</v>
+        <v>184</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>621</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>516</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>624</v>
@@ -7703,7 +7703,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>628</v>
@@ -7714,29 +7714,29 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>630</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>408</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>631</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>411</v>
+        <v>314</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>632</v>
@@ -7747,7 +7747,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>632</v>
@@ -7758,7 +7758,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>632</v>
@@ -7769,29 +7769,29 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>632</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>532</v>
+        <v>274</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>632</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>415</v>
+        <v>298</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>636</v>
@@ -7802,18 +7802,18 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>638</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>421</v>
+        <v>309</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>639</v>
@@ -7824,7 +7824,7 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>641</v>
@@ -7835,7 +7835,7 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>641</v>
@@ -7846,7 +7846,7 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>641</v>
@@ -7857,7 +7857,7 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>641</v>
@@ -7868,7 +7868,7 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>641</v>
@@ -7879,7 +7879,7 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>647</v>
@@ -7890,7 +7890,7 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>647</v>
@@ -7901,18 +7901,18 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>650</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>281</v>
+        <v>354</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>651</v>
@@ -7923,18 +7923,18 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>651</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>283</v>
+        <v>360</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>651</v>
@@ -7945,7 +7945,7 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>651</v>
@@ -7956,7 +7956,7 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>116</v>
+        <v>366</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>655</v>
@@ -7967,7 +7967,7 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>116</v>
+        <v>366</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>657</v>
@@ -7978,7 +7978,7 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>659</v>
@@ -7989,7 +7989,7 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>661</v>
@@ -8000,7 +8000,7 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>663</v>
@@ -8011,7 +8011,7 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>665</v>
@@ -8022,7 +8022,7 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>667</v>
@@ -8033,7 +8033,7 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>669</v>
@@ -8044,7 +8044,7 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>671</v>
@@ -8055,7 +8055,7 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>667</v>
@@ -8066,7 +8066,7 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>674</v>
@@ -8077,7 +8077,7 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>674</v>
@@ -8088,7 +8088,7 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>677</v>
@@ -8099,7 +8099,7 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>674</v>
@@ -8110,7 +8110,7 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>674</v>
@@ -8121,7 +8121,7 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>677</v>
@@ -8132,7 +8132,7 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>674</v>
@@ -8143,7 +8143,7 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>677</v>
@@ -8154,7 +8154,7 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>674</v>
@@ -8165,7 +8165,7 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>677</v>
@@ -8176,7 +8176,7 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>674</v>
@@ -8187,7 +8187,7 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>674</v>
@@ -8198,7 +8198,7 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>677</v>
@@ -8209,7 +8209,7 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>674</v>
@@ -8220,7 +8220,7 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>674</v>
@@ -8231,7 +8231,7 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>677</v>
@@ -8242,7 +8242,7 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>674</v>
@@ -8253,7 +8253,7 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>693</v>
@@ -8264,7 +8264,7 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>677</v>
